--- a/data/exports/observatorio_depositos_judiciais.xlsx
+++ b/data/exports/observatorio_depositos_judiciais.xlsx
@@ -437,14 +437,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gerado em (UTC): 2026-08-19T14:44:57+00:00</t>
+          <t>Gerado em (UTC): 2026-09-05T12:16:24+00:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Última data-base: 202603</t>
+          <t>Última data-base: 202605</t>
         </is>
       </c>
     </row>
@@ -2240,7 +2240,11 @@
           <t>https://www.bcb.gov.br/content/estabilidadefinanceira/cosif/Bancos/202604BANCOS.csv.zip</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>data/raw/bcb_balancetes/202604BANCOS.csv.zip</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>202604</t>
@@ -2248,14 +2252,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-08-19T14:44:53+00:00</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+          <t>2026-09-05T12:16:21+00:00</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>943695</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>nao_disponivel</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2290,11 @@
           <t>https://www.bcb.gov.br/content/estabilidadefinanceira/cosif/Bancos/202605BANCOS.csv.zip</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>data/raw/bcb_balancetes/202605BANCOS.csv.zip</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>202605</t>
@@ -2288,14 +2302,20 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-08-19T14:44:55+00:00</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+          <t>2026-09-05T12:16:22+00:00</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>947822</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>nao_disponivel</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2652,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15 meses no staging (202501–202603); nao disponiveis: ['202604', '202605']</t>
+          <t>17 meses no staging (202501–202605); nao disponiveis: nenhum</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3359,6 +3379,92 @@
         <v>5071.253178046866</v>
       </c>
       <c r="M16" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>441835589379.88</v>
+      </c>
+      <c r="C17" t="n">
+        <v>400845386107.65</v>
+      </c>
+      <c r="D17" t="n">
+        <v>77955744011.22</v>
+      </c>
+      <c r="E17" t="n">
+        <v>24027865148.55</v>
+      </c>
+      <c r="F17" t="n">
+        <v>13</v>
+      </c>
+      <c r="G17" t="n">
+        <v>502828995267.42</v>
+      </c>
+      <c r="H17" t="n">
+        <v>944664584647.3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.6503804131643038</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.9575932677224864</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.998316975177478</v>
+      </c>
+      <c r="L17" t="n">
+        <v>5181.438652922216</v>
+      </c>
+      <c r="M17" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>434003495787.1099</v>
+      </c>
+      <c r="C18" t="n">
+        <v>403449882590.66</v>
+      </c>
+      <c r="D18" t="n">
+        <v>78140436512.17</v>
+      </c>
+      <c r="E18" t="n">
+        <v>24062714606.79</v>
+      </c>
+      <c r="F18" t="n">
+        <v>13</v>
+      </c>
+      <c r="G18" t="n">
+        <v>505653033709.6199</v>
+      </c>
+      <c r="H18" t="n">
+        <v>939656529496.73</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.6536178091936355</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.9568165068243754</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.9982813284893544</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5199.442454085088</v>
+      </c>
+      <c r="M18" t="n">
         <v>13</v>
       </c>
     </row>
@@ -3373,7 +3479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W206"/>
+  <dimension ref="A1:W232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19645,6 +19751,2052 @@
       <c r="W206" t="inlineStr">
         <is>
           <t>Mercantil do Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>00000000</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>BCO DO BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>287361213171.58</v>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="n">
+        <v>62852309883.22</v>
+      </c>
+      <c r="G207" t="n">
+        <v>22413895321.71</v>
+      </c>
+      <c r="H207" t="n">
+        <v>-9713721199.950001</v>
+      </c>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="n">
+        <v>2486649873297.67</v>
+      </c>
+      <c r="K207" t="n">
+        <v>934743768586.55</v>
+      </c>
+      <c r="L207" t="n">
+        <v>2031525678675.3</v>
+      </c>
+      <c r="M207" t="n">
+        <v>183607032259.42</v>
+      </c>
+      <c r="N207" t="n">
+        <v>372627418376.5101</v>
+      </c>
+      <c r="O207" t="n">
+        <v>0.115561590016087</v>
+      </c>
+      <c r="P207" t="n">
+        <v>0.3074224432713857</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>0.1414509381732059</v>
+      </c>
+      <c r="R207" t="n">
+        <v>1.565088273773549</v>
+      </c>
+      <c r="S207" t="n">
+        <v>2.029483368861501</v>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>publico_federal</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>Banco do Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>00360305</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>CAIXA ECONOMICA FEDERAL</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>135737572658.79</v>
+      </c>
+      <c r="E208" t="n">
+        <v>400845386107.65</v>
+      </c>
+      <c r="F208" t="n">
+        <v>4597796002.82</v>
+      </c>
+      <c r="G208" t="n">
+        <v>1059811536.53</v>
+      </c>
+      <c r="H208" t="n">
+        <v>-3805410390.29</v>
+      </c>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="n">
+        <v>2353332972881.29</v>
+      </c>
+      <c r="K208" t="n">
+        <v>867047482497.14</v>
+      </c>
+      <c r="L208" t="n">
+        <v>2131887967930.96</v>
+      </c>
+      <c r="M208" t="n">
+        <v>111826905526.51</v>
+      </c>
+      <c r="N208" t="n">
+        <v>542240566305.7901</v>
+      </c>
+      <c r="O208" t="n">
+        <v>0.0576788640719211</v>
+      </c>
+      <c r="P208" t="n">
+        <v>0.1565514869703087</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>0.06367012465037079</v>
+      </c>
+      <c r="R208" t="n">
+        <v>1.213818553054852</v>
+      </c>
+      <c r="S208" t="n">
+        <v>4.848927579215228</v>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>publico_federal</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>Caixa</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>92702067</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>BCO DO ESTADO DO RS S.A.</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>11040046942.05</v>
+      </c>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="n">
+        <v>10306349442.94</v>
+      </c>
+      <c r="G209" t="n">
+        <v>113936934.05</v>
+      </c>
+      <c r="H209" t="n">
+        <v>-312039802.39</v>
+      </c>
+      <c r="I209" t="inlineStr"/>
+      <c r="J209" t="n">
+        <v>166903835260.05</v>
+      </c>
+      <c r="K209" t="n">
+        <v>104474185586.57</v>
+      </c>
+      <c r="L209" t="n">
+        <v>146898549707.33</v>
+      </c>
+      <c r="M209" t="n">
+        <v>11099840009.41</v>
+      </c>
+      <c r="N209" t="n">
+        <v>21460333319.04</v>
+      </c>
+      <c r="O209" t="n">
+        <v>0.0661461549091948</v>
+      </c>
+      <c r="P209" t="n">
+        <v>0.1056724862708016</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>0.07515422694128281</v>
+      </c>
+      <c r="R209" t="n">
+        <v>0.9946131595311904</v>
+      </c>
+      <c r="S209" t="n">
+        <v>1.933391229139049</v>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>publico_estadual</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>Banrisul</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>28127603</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>BCO BANESTES S.A.</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>4891323421.51</v>
+      </c>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="n">
+        <v>426196448.08</v>
+      </c>
+      <c r="H210" t="n">
+        <v>-187492196.45</v>
+      </c>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" t="n">
+        <v>41467312789.58</v>
+      </c>
+      <c r="K210" t="n">
+        <v>26206995230.47</v>
+      </c>
+      <c r="L210" t="n">
+        <v>37533522934.29</v>
+      </c>
+      <c r="M210" t="n">
+        <v>2341227010.18</v>
+      </c>
+      <c r="N210" t="n">
+        <v>5317519869.59</v>
+      </c>
+      <c r="O210" t="n">
+        <v>0.1179561223639044</v>
+      </c>
+      <c r="P210" t="n">
+        <v>0.1866419014654156</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>0.1303187934176402</v>
+      </c>
+      <c r="R210" t="n">
+        <v>2.089213647477073</v>
+      </c>
+      <c r="S210" t="n">
+        <v>2.271253426715411</v>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>publico_estadual</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>Banestes</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>13009717</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>BCO DO EST. DE SE S.A.</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>2061812921.55</v>
+      </c>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="n">
+        <v>199288682.24</v>
+      </c>
+      <c r="G211" t="n">
+        <v>14024908.18</v>
+      </c>
+      <c r="H211" t="n">
+        <v>-64140462.92</v>
+      </c>
+      <c r="I211" t="n">
+        <v>-19448.45</v>
+      </c>
+      <c r="J211" t="n">
+        <v>13100443971.46</v>
+      </c>
+      <c r="K211" t="n">
+        <v>11145344070.03</v>
+      </c>
+      <c r="L211" t="n">
+        <v>11774393328.65</v>
+      </c>
+      <c r="M211" t="n">
+        <v>920538843.88</v>
+      </c>
+      <c r="N211" t="n">
+        <v>2275126511.97</v>
+      </c>
+      <c r="O211" t="n">
+        <v>0.1573849654287875</v>
+      </c>
+      <c r="P211" t="n">
+        <v>0.1849932051083327</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>0.1751099070669824</v>
+      </c>
+      <c r="R211" t="n">
+        <v>2.2397891574674</v>
+      </c>
+      <c r="S211" t="n">
+        <v>2.47151603334903</v>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>publico_estadual</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>Banese</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>60746948</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>BCO BRADESCO S.A.</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>281906431.24</v>
+      </c>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="n">
+        <v>-7389416.37</v>
+      </c>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="n">
+        <v>1941523073613.29</v>
+      </c>
+      <c r="K212" t="n">
+        <v>692827996231.08</v>
+      </c>
+      <c r="L212" t="n">
+        <v>1587595592312.26</v>
+      </c>
+      <c r="M212" t="n">
+        <v>166489615185.87</v>
+      </c>
+      <c r="N212" t="n">
+        <v>281906431.24</v>
+      </c>
+      <c r="O212" t="n">
+        <v>0.000145198599528</v>
+      </c>
+      <c r="P212" t="n">
+        <v>0.0004068923784453</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>0.0001775681619457</v>
+      </c>
+      <c r="R212" t="n">
+        <v>0.0016932373284981</v>
+      </c>
+      <c r="S212" t="n">
+        <v>0.0016932373284981</v>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>privado</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>Bradesco</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>07237373</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>BCO DO NORDESTE DO BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>208209265.49</v>
+      </c>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="n">
+        <v>-5292533.02</v>
+      </c>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="n">
+        <v>75619541647.75999</v>
+      </c>
+      <c r="K213" t="n">
+        <v>14066836953.14</v>
+      </c>
+      <c r="L213" t="n">
+        <v>26699191132.68</v>
+      </c>
+      <c r="M213" t="n">
+        <v>16127238662.94</v>
+      </c>
+      <c r="N213" t="n">
+        <v>208209265.49</v>
+      </c>
+      <c r="O213" t="n">
+        <v>0.0027533790995434</v>
+      </c>
+      <c r="P213" t="n">
+        <v>0.0148014273701753</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>0.0077983360789964</v>
+      </c>
+      <c r="R213" t="n">
+        <v>0.0129104101353978</v>
+      </c>
+      <c r="S213" t="n">
+        <v>0.0129104101353978</v>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>publico_federal</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>Banco do Nordeste</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>90400888</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>BCO SANTANDER (BRASIL) S.A.</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>139996420.21</v>
+      </c>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="n">
+        <v>-3635578.86</v>
+      </c>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="n">
+        <v>1216327810056.96</v>
+      </c>
+      <c r="K214" t="n">
+        <v>461635339895.41</v>
+      </c>
+      <c r="L214" t="n">
+        <v>968223489807.5699</v>
+      </c>
+      <c r="M214" t="n">
+        <v>91475191253.39</v>
+      </c>
+      <c r="N214" t="n">
+        <v>139996420.21</v>
+      </c>
+      <c r="O214" t="n">
+        <v>0.0001150976069546</v>
+      </c>
+      <c r="P214" t="n">
+        <v>0.0003032619215021</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>0.0001445910181726</v>
+      </c>
+      <c r="R214" t="n">
+        <v>0.0015304304729159</v>
+      </c>
+      <c r="S214" t="n">
+        <v>0.0015304304729159</v>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>privado</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>04902979</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>BCO DA AMAZONIA S.A.</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>92974996.94</v>
+      </c>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="n">
+        <v>-2397872.61</v>
+      </c>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="n">
+        <v>65970483354.55</v>
+      </c>
+      <c r="K215" t="n">
+        <v>13088430032.37</v>
+      </c>
+      <c r="L215" t="n">
+        <v>15287646098.61</v>
+      </c>
+      <c r="M215" t="n">
+        <v>7132870340.13</v>
+      </c>
+      <c r="N215" t="n">
+        <v>92974996.94</v>
+      </c>
+      <c r="O215" t="n">
+        <v>0.0014093423636191</v>
+      </c>
+      <c r="P215" t="n">
+        <v>0.0071036019377462</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>0.0060817078273713</v>
+      </c>
+      <c r="R215" t="n">
+        <v>0.0130347241021495</v>
+      </c>
+      <c r="S215" t="n">
+        <v>0.0130347241021495</v>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>publico_federal</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>Banco da Amazônia</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>60701190</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>ITAÚ UNIBANCO S.A.</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>17593597.75</v>
+      </c>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="n">
+        <v>-467125.57</v>
+      </c>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="n">
+        <v>2156206972283.6</v>
+      </c>
+      <c r="K216" t="n">
+        <v>832016249096.5601</v>
+      </c>
+      <c r="L216" t="n">
+        <v>1867526736481.28</v>
+      </c>
+      <c r="M216" t="n">
+        <v>147578045519.6</v>
+      </c>
+      <c r="N216" t="n">
+        <v>17593597.75</v>
+      </c>
+      <c r="O216" t="n">
+        <v>8.159512503276499e-06</v>
+      </c>
+      <c r="P216" t="n">
+        <v>2.114573816208987e-05</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>9.42080100183688e-06</v>
+      </c>
+      <c r="R216" t="n">
+        <v>0.0001192155492238</v>
+      </c>
+      <c r="S216" t="n">
+        <v>0.0001192155492238</v>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>privado</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>Itaú Unibanco</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>28195667</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>BCO ABC BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>1741353.29</v>
+      </c>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="n">
+        <v>-45190.54</v>
+      </c>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="n">
+        <v>64988665111.65</v>
+      </c>
+      <c r="K217" t="n">
+        <v>8053782083.12</v>
+      </c>
+      <c r="L217" t="n">
+        <v>51289295322.5</v>
+      </c>
+      <c r="M217" t="n">
+        <v>6870779007.95</v>
+      </c>
+      <c r="N217" t="n">
+        <v>1741353.29</v>
+      </c>
+      <c r="O217" t="n">
+        <v>2.679472315685157e-05</v>
+      </c>
+      <c r="P217" t="n">
+        <v>0.0002162155956081</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>3.395159319406927e-05</v>
+      </c>
+      <c r="R217" t="n">
+        <v>0.0002534433559841</v>
+      </c>
+      <c r="S217" t="n">
+        <v>0.0002534433559841</v>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>privado</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>ABC Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>17184037</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>BCO MERCANTIL DO BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>894076.38</v>
+      </c>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="n">
+        <v>-4065.53</v>
+      </c>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="n">
+        <v>41065074817.9</v>
+      </c>
+      <c r="K218" t="n">
+        <v>21233934986.58</v>
+      </c>
+      <c r="L218" t="n">
+        <v>31697786136.14</v>
+      </c>
+      <c r="M218" t="n">
+        <v>2698206584.11</v>
+      </c>
+      <c r="N218" t="n">
+        <v>894076.38</v>
+      </c>
+      <c r="O218" t="n">
+        <v>2.177218436748782e-05</v>
+      </c>
+      <c r="P218" t="n">
+        <v>4.210601476198654e-05</v>
+      </c>
+      <c r="Q218" t="n">
+        <v>2.820627207717278e-05</v>
+      </c>
+      <c r="R218" t="n">
+        <v>0.0003313594982924</v>
+      </c>
+      <c r="S218" t="n">
+        <v>0.0003313594982924</v>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>privado</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>Mercantil do Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>04913711</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>BCO DO EST. DO PA S.A.</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>304123.1</v>
+      </c>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="n">
+        <v>-1413.57</v>
+      </c>
+      <c r="I219" t="inlineStr"/>
+      <c r="J219" t="n">
+        <v>19937314113.54</v>
+      </c>
+      <c r="K219" t="n">
+        <v>14018546811.37</v>
+      </c>
+      <c r="L219" t="n">
+        <v>16945915538.6</v>
+      </c>
+      <c r="M219" t="n">
+        <v>2172653434.29</v>
+      </c>
+      <c r="N219" t="n">
+        <v>304123.1</v>
+      </c>
+      <c r="O219" t="n">
+        <v>1.52539654172104e-05</v>
+      </c>
+      <c r="P219" t="n">
+        <v>2.169433851398458e-05</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>1.79466904167708e-05</v>
+      </c>
+      <c r="R219" t="n">
+        <v>0.0001399777319291</v>
+      </c>
+      <c r="S219" t="n">
+        <v>0.0001399777319291</v>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>publico_estadual</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>Banpará</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>00000000</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>BCO DO BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>283672414098.75</v>
+      </c>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="n">
+        <v>63016979705.95</v>
+      </c>
+      <c r="G220" t="n">
+        <v>22445376770.16</v>
+      </c>
+      <c r="H220" t="n">
+        <v>-12257536052.96</v>
+      </c>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="n">
+        <v>2453867168273.74</v>
+      </c>
+      <c r="K220" t="n">
+        <v>935689001095.02</v>
+      </c>
+      <c r="L220" t="n">
+        <v>1995746139697.01</v>
+      </c>
+      <c r="M220" t="n">
+        <v>183054562618.11</v>
+      </c>
+      <c r="N220" t="n">
+        <v>369134770574.86</v>
+      </c>
+      <c r="O220" t="n">
+        <v>0.1156021881568713</v>
+      </c>
+      <c r="P220" t="n">
+        <v>0.3031695507447167</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>0.1421385257655147</v>
+      </c>
+      <c r="R220" t="n">
+        <v>1.54966044026201</v>
+      </c>
+      <c r="S220" t="n">
+        <v>2.01652865296208</v>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>publico_federal</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>Banco do Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>00360305</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>CAIXA ECONOMICA FEDERAL</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>131589294689.84</v>
+      </c>
+      <c r="E221" t="n">
+        <v>403449882590.66</v>
+      </c>
+      <c r="F221" t="n">
+        <v>4618767253.95</v>
+      </c>
+      <c r="G221" t="n">
+        <v>1058263932.24</v>
+      </c>
+      <c r="H221" t="n">
+        <v>-4779349200.39</v>
+      </c>
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="n">
+        <v>2360243055302.2</v>
+      </c>
+      <c r="K221" t="n">
+        <v>875829465868.5601</v>
+      </c>
+      <c r="L221" t="n">
+        <v>2139292092368.85</v>
+      </c>
+      <c r="M221" t="n">
+        <v>111795260363.87</v>
+      </c>
+      <c r="N221" t="n">
+        <v>540716208466.69</v>
+      </c>
+      <c r="O221" t="n">
+        <v>0.0557524337988112</v>
+      </c>
+      <c r="P221" t="n">
+        <v>0.1502453386394609</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>0.0615106722262178</v>
+      </c>
+      <c r="R221" t="n">
+        <v>1.177056113663</v>
+      </c>
+      <c r="S221" t="n">
+        <v>4.836664870288533</v>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>publico_federal</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>Caixa</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>92702067</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>BCO DO ESTADO DO RS S.A.</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>11046442326.66</v>
+      </c>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="n">
+        <v>10306349442.94</v>
+      </c>
+      <c r="G222" t="n">
+        <v>116622047.86</v>
+      </c>
+      <c r="H222" t="n">
+        <v>-390373703.05</v>
+      </c>
+      <c r="I222" t="inlineStr"/>
+      <c r="J222" t="n">
+        <v>169061119644.77</v>
+      </c>
+      <c r="K222" t="n">
+        <v>106097437022.73</v>
+      </c>
+      <c r="L222" t="n">
+        <v>149096465715.5</v>
+      </c>
+      <c r="M222" t="n">
+        <v>11103046502.99</v>
+      </c>
+      <c r="N222" t="n">
+        <v>21469413817.46</v>
+      </c>
+      <c r="O222" t="n">
+        <v>0.0653399335688223</v>
+      </c>
+      <c r="P222" t="n">
+        <v>0.1041160148316631</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>0.0740892299066188</v>
+      </c>
+      <c r="R222" t="n">
+        <v>0.9949019238715467</v>
+      </c>
+      <c r="S222" t="n">
+        <v>1.933650715745303</v>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>publico_estadual</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>Banrisul</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>28127603</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>BCO BANESTES S.A.</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>4904891924.94</v>
+      </c>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="n">
+        <v>428365573.71</v>
+      </c>
+      <c r="H223" t="n">
+        <v>-232751921.58</v>
+      </c>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="n">
+        <v>42657067833.39</v>
+      </c>
+      <c r="K223" t="n">
+        <v>26759171374.5</v>
+      </c>
+      <c r="L223" t="n">
+        <v>38673123183.07</v>
+      </c>
+      <c r="M223" t="n">
+        <v>2327141523.31</v>
+      </c>
+      <c r="N223" t="n">
+        <v>5333257498.65</v>
+      </c>
+      <c r="O223" t="n">
+        <v>0.1149842728079091</v>
+      </c>
+      <c r="P223" t="n">
+        <v>0.183297601270796</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>0.1268294753884067</v>
+      </c>
+      <c r="R223" t="n">
+        <v>2.107689573586203</v>
+      </c>
+      <c r="S223" t="n">
+        <v>2.291763283508544</v>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>publico_estadual</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>Banestes</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>13009717</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>BCO DO EST. DE SE S.A.</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>2044543303.19</v>
+      </c>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="n">
+        <v>198340109.33</v>
+      </c>
+      <c r="G224" t="n">
+        <v>14086282.82</v>
+      </c>
+      <c r="H224" t="n">
+        <v>-79123524.78</v>
+      </c>
+      <c r="I224" t="n">
+        <v>-19162.72</v>
+      </c>
+      <c r="J224" t="n">
+        <v>13303782998.27</v>
+      </c>
+      <c r="K224" t="n">
+        <v>11315093621.84</v>
+      </c>
+      <c r="L224" t="n">
+        <v>11957840179.7</v>
+      </c>
+      <c r="M224" t="n">
+        <v>920538843.88</v>
+      </c>
+      <c r="N224" t="n">
+        <v>2256969695.34</v>
+      </c>
+      <c r="O224" t="n">
+        <v>0.1536813478884817</v>
+      </c>
+      <c r="P224" t="n">
+        <v>0.1806916824129226</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>0.1709793133596885</v>
+      </c>
+      <c r="R224" t="n">
+        <v>2.221028821089622</v>
+      </c>
+      <c r="S224" t="n">
+        <v>2.451791915512275</v>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>publico_estadual</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>Banese</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>60746948</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>BCO BRADESCO S.A.</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>283776803.35</v>
+      </c>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="n">
+        <v>-9284050.699999999</v>
+      </c>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="n">
+        <v>1931867573693.73</v>
+      </c>
+      <c r="K225" t="n">
+        <v>699612100313.48</v>
+      </c>
+      <c r="L225" t="n">
+        <v>1585196817920.14</v>
+      </c>
+      <c r="M225" t="n">
+        <v>164790233511.79</v>
+      </c>
+      <c r="N225" t="n">
+        <v>283776803.35</v>
+      </c>
+      <c r="O225" t="n">
+        <v>0.0001468924719345</v>
+      </c>
+      <c r="P225" t="n">
+        <v>0.0004056202047146</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>0.0001790167631817</v>
+      </c>
+      <c r="R225" t="n">
+        <v>0.0017220486754738</v>
+      </c>
+      <c r="S225" t="n">
+        <v>0.0017220486754738</v>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>privado</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>Bradesco</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>07237373</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>BCO DO NORDESTE DO BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>210235899.58</v>
+      </c>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="n">
+        <v>-6669143.44</v>
+      </c>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="n">
+        <v>77975283057.84</v>
+      </c>
+      <c r="K226" t="n">
+        <v>14528483517.19</v>
+      </c>
+      <c r="L226" t="n">
+        <v>27239014907.4</v>
+      </c>
+      <c r="M226" t="n">
+        <v>16122209193.96</v>
+      </c>
+      <c r="N226" t="n">
+        <v>210235899.58</v>
+      </c>
+      <c r="O226" t="n">
+        <v>0.002696186423896</v>
+      </c>
+      <c r="P226" t="n">
+        <v>0.014470601789323</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>0.0077181902610907</v>
+      </c>
+      <c r="R226" t="n">
+        <v>0.0130401421449588</v>
+      </c>
+      <c r="S226" t="n">
+        <v>0.0130401421449588</v>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>publico_federal</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>Banco do Nordeste</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>90400888</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>BCO SANTANDER (BRASIL) S.A.</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>140601826.07</v>
+      </c>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="n">
+        <v>-4547516.82</v>
+      </c>
+      <c r="I227" t="inlineStr"/>
+      <c r="J227" t="n">
+        <v>1243803525521.9</v>
+      </c>
+      <c r="K227" t="n">
+        <v>468600549204.98</v>
+      </c>
+      <c r="L227" t="n">
+        <v>973730599169.75</v>
+      </c>
+      <c r="M227" t="n">
+        <v>91421261636.09</v>
+      </c>
+      <c r="N227" t="n">
+        <v>140601826.07</v>
+      </c>
+      <c r="O227" t="n">
+        <v>0.0001130418295051</v>
+      </c>
+      <c r="P227" t="n">
+        <v>0.0003000462255294</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>0.0001443949961004</v>
+      </c>
+      <c r="R227" t="n">
+        <v>0.0015379554334928</v>
+      </c>
+      <c r="S227" t="n">
+        <v>0.0015379554334928</v>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>privado</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>04902979</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>BCO DA AMAZONIA S.A.</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>90338336.5</v>
+      </c>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="n">
+        <v>-2951559.95</v>
+      </c>
+      <c r="I228" t="inlineStr"/>
+      <c r="J228" t="n">
+        <v>66810986128.45</v>
+      </c>
+      <c r="K228" t="n">
+        <v>13116139758.01</v>
+      </c>
+      <c r="L228" t="n">
+        <v>15342486459.74</v>
+      </c>
+      <c r="M228" t="n">
+        <v>7123480159.58</v>
+      </c>
+      <c r="N228" t="n">
+        <v>90338336.5</v>
+      </c>
+      <c r="O228" t="n">
+        <v>0.0013521479285804</v>
+      </c>
+      <c r="P228" t="n">
+        <v>0.0068875704412062</v>
+      </c>
+      <c r="Q228" t="n">
+        <v>0.0058881157716551</v>
+      </c>
+      <c r="R228" t="n">
+        <v>0.0126817699321459</v>
+      </c>
+      <c r="S228" t="n">
+        <v>0.0126817699321459</v>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>publico_federal</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>Banco da Amazônia</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>60701190</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>ITAÚ UNIBANCO S.A.</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>17705955.24</v>
+      </c>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="n">
+        <v>-579483.0600000001</v>
+      </c>
+      <c r="I229" t="inlineStr"/>
+      <c r="J229" t="n">
+        <v>2135405793895.84</v>
+      </c>
+      <c r="K229" t="n">
+        <v>847989122324.5699</v>
+      </c>
+      <c r="L229" t="n">
+        <v>1854092744453.18</v>
+      </c>
+      <c r="M229" t="n">
+        <v>148144561219.9</v>
+      </c>
+      <c r="N229" t="n">
+        <v>17705955.24</v>
+      </c>
+      <c r="O229" t="n">
+        <v>8.291611501014619e-06</v>
+      </c>
+      <c r="P229" t="n">
+        <v>2.087993203434395e-05</v>
+      </c>
+      <c r="Q229" t="n">
+        <v>9.549659957933737e-06</v>
+      </c>
+      <c r="R229" t="n">
+        <v>0.000119518091614</v>
+      </c>
+      <c r="S229" t="n">
+        <v>0.000119518091614</v>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>privado</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>Itaú Unibanco</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>28195667</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>BCO ABC BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>1753305.48</v>
+      </c>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="n">
+        <v>-57142.73</v>
+      </c>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="n">
+        <v>66607397350.75</v>
+      </c>
+      <c r="K230" t="n">
+        <v>8385359783.33</v>
+      </c>
+      <c r="L230" t="n">
+        <v>53141183264.47</v>
+      </c>
+      <c r="M230" t="n">
+        <v>6818518751.24</v>
+      </c>
+      <c r="N230" t="n">
+        <v>1753305.48</v>
+      </c>
+      <c r="O230" t="n">
+        <v>2.632298437915556e-05</v>
+      </c>
+      <c r="P230" t="n">
+        <v>0.0002090912644542</v>
+      </c>
+      <c r="Q230" t="n">
+        <v>3.299334663427138e-05</v>
+      </c>
+      <c r="R230" t="n">
+        <v>0.0002571387634126</v>
+      </c>
+      <c r="S230" t="n">
+        <v>0.0002571387634126</v>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>privado</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>ABC Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>17184037</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>BCO MERCANTIL DO BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>900224.95</v>
+      </c>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="n">
+        <v>-7010.15</v>
+      </c>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="n">
+        <v>42095156784.78</v>
+      </c>
+      <c r="K231" t="n">
+        <v>21757624436.67</v>
+      </c>
+      <c r="L231" t="n">
+        <v>32427253733.33</v>
+      </c>
+      <c r="M231" t="n">
+        <v>2649032754.81</v>
+      </c>
+      <c r="N231" t="n">
+        <v>900224.95</v>
+      </c>
+      <c r="O231" t="n">
+        <v>2.138547564040638e-05</v>
+      </c>
+      <c r="P231" t="n">
+        <v>4.137514886426541e-05</v>
+      </c>
+      <c r="Q231" t="n">
+        <v>2.776136879808337e-05</v>
+      </c>
+      <c r="R231" t="n">
+        <v>0.0003398315662067</v>
+      </c>
+      <c r="S231" t="n">
+        <v>0.0003398315662067</v>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>privado</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>Mercantil do Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>04913711</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>BCO DO EST. DO PA S.A.</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>597092.5600000001</v>
+      </c>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="n">
+        <v>-1748.73</v>
+      </c>
+      <c r="I232" t="inlineStr"/>
+      <c r="J232" t="n">
+        <v>20665619975.2</v>
+      </c>
+      <c r="K232" t="n">
+        <v>14734625044.03</v>
+      </c>
+      <c r="L232" t="n">
+        <v>17716943185.66</v>
+      </c>
+      <c r="M232" t="n">
+        <v>2143574552.34</v>
+      </c>
+      <c r="N232" t="n">
+        <v>597092.5600000001</v>
+      </c>
+      <c r="O232" t="n">
+        <v>2.889303881115337e-05</v>
+      </c>
+      <c r="P232" t="n">
+        <v>4.052309157618659e-05</v>
+      </c>
+      <c r="Q232" t="n">
+        <v>3.370178217217988e-05</v>
+      </c>
+      <c r="R232" t="n">
+        <v>0.0002785499386285</v>
+      </c>
+      <c r="S232" t="n">
+        <v>0.0002785499386285</v>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>publico_estadual</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>n/d</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>Banpará</t>
         </is>
       </c>
     </row>
@@ -19659,7 +21811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I171"/>
+  <dimension ref="A1:I191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27016,6 +29168,866 @@
       <c r="I171" t="inlineStr">
         <is>
           <t>7182290443ade7d8de26c8e0522ac2ae946a754f88065037725421b32441571d</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>28127603</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>BCO BANESTES S.A.</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Municipios</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>9090900001</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>426196448.08</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H172" t="n">
+        <v>21172</v>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>00000000</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>BCO DO BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Estados e DF</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>9090800008</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>62852309883.22</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H173" t="n">
+        <v>617</v>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>00000000</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>BCO DO BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Municipios</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>9090900001</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>22413895321.71</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H174" t="n">
+        <v>618</v>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>13009717</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>BCO DO EST. DE SE S.A.</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Estados e DF</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>9090800008</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>199288682.24</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H175" t="n">
+        <v>16201</v>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>13009717</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>BCO DO EST. DE SE S.A.</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Municipios</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>9090900001</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>14024908.18</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H176" t="n">
+        <v>16202</v>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>92702067</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>BCO DO ESTADO DO RS S.A.</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Estados e DF</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>9090800008</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>10306349442.94</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H177" t="n">
+        <v>49515</v>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>92702067</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>BCO DO ESTADO DO RS S.A.</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Municipios</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>9090900001</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>113936934.05</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H178" t="n">
+        <v>49516</v>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>00360305</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>CAIXA ECONOMICA FEDERAL</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Uniao</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>9090700005</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>400845386107.65</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H179" t="n">
+        <v>1240</v>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>00360305</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>CAIXA ECONOMICA FEDERAL</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Estados e DF</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>9090800008</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>4597796002.82</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H180" t="n">
+        <v>1241</v>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>00360305</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>CAIXA ECONOMICA FEDERAL</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Municipios</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>9090900001</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>1059811536.53</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H181" t="n">
+        <v>1242</v>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>28127603</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>BCO BANESTES S.A.</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Municipios</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>9090900001</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>428365573.71</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H182" t="n">
+        <v>21327</v>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>00000000</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>BCO DO BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Estados e DF</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>9090800008</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>63016979705.95</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H183" t="n">
+        <v>613</v>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>00000000</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>BCO DO BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Municipios</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>9090900001</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>22445376770.16</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H184" t="n">
+        <v>614</v>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>13009717</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>BCO DO EST. DE SE S.A.</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Estados e DF</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>9090800008</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>198340109.33</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H185" t="n">
+        <v>16296</v>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>13009717</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>BCO DO EST. DE SE S.A.</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Municipios</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>9090900001</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>14086282.82</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H186" t="n">
+        <v>16297</v>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>92702067</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>BCO DO ESTADO DO RS S.A.</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Estados e DF</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>9090800008</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>10306349442.94</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H187" t="n">
+        <v>49497</v>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>92702067</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>BCO DO ESTADO DO RS S.A.</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Municipios</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>9090900001</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>116622047.86</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H188" t="n">
+        <v>49498</v>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>00360305</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>CAIXA ECONOMICA FEDERAL</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Uniao</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>9090700005</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>403449882590.66</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H189" t="n">
+        <v>1235</v>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>00360305</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>CAIXA ECONOMICA FEDERAL</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Estados e DF</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>9090800008</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>4618767253.95</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H190" t="n">
+        <v>1236</v>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>00360305</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>CAIXA ECONOMICA FEDERAL</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Municipios</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>9090900001</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>1058263932.24</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H191" t="n">
+        <v>1237</v>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
         </is>
       </c>
     </row>
@@ -27030,7 +30042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J651"/>
+  <dimension ref="A1:J733"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58280,6 +61292,3942 @@
         </is>
       </c>
       <c r="J651" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>50585090</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>BANCO BMG CONSIGNADO S.A.</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>1899800001</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>(-) PROVISÃO PARA PERDAS DE CRÉDITO EM RESTITUIÇÃO DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS</t>
+        </is>
+      </c>
+      <c r="F652" t="n">
+        <v>-155.54</v>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H652" t="n">
+        <v>32348</v>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J652" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>62421979</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>BANCO BMG SOLUÇÕES FINANCEIRAS S.A.</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>1899800001</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>(-) PROVISÃO PARA PERDAS DE CRÉDITO EM RESTITUIÇÃO DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS</t>
+        </is>
+      </c>
+      <c r="F653" t="n">
+        <v>-235.33</v>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H653" t="n">
+        <v>45495</v>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J653" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>92894922</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>BANCO ORIGINAL</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>1899800001</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>(-) PROVISÃO PARA PERDAS DE CRÉDITO EM RESTITUIÇÃO DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS</t>
+        </is>
+      </c>
+      <c r="F654" t="n">
+        <v>-4929.1</v>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H654" t="n">
+        <v>50232</v>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J654" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>28195667</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>BCO ABC BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>4155000009</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F655" t="n">
+        <v>1741353.29</v>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H655" t="n">
+        <v>21711</v>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J655" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>28195667</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>BCO ABC BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>8114000008</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F656" t="n">
+        <v>-45190.54</v>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H656" t="n">
+        <v>21853</v>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J656" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>28127603</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>BCO BANESTES S.A.</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>4155000009</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F657" t="n">
+        <v>4891323421.51</v>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H657" t="n">
+        <v>20962</v>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J657" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>28127603</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>BCO BANESTES S.A.</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>8114000008</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F658" t="n">
+        <v>-187492196.45</v>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H658" t="n">
+        <v>21097</v>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J658" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>28127603</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>BCO BANESTES S.A.</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>9090900001</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS REPASSADOS A MUNICÍPIOS</t>
+        </is>
+      </c>
+      <c r="F659" t="n">
+        <v>426196448.08</v>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H659" t="n">
+        <v>21172</v>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J659" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>61186680</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>BCO BMG S.A.</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>1899800001</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>(-) PROVISÃO PARA PERDAS DE CRÉDITO EM RESTITUIÇÃO DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS</t>
+        </is>
+      </c>
+      <c r="F660" t="n">
+        <v>-516102.99</v>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H660" t="n">
+        <v>41677</v>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J660" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>60746948</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>BCO BRADESCO S.A.</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>4155000009</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F661" t="n">
+        <v>281906431.24</v>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H661" t="n">
+        <v>38653</v>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J661" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>60746948</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>BCO BRADESCO S.A.</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>8114000008</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F662" t="n">
+        <v>-7389416.37</v>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H662" t="n">
+        <v>38861</v>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J662" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>04902979</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>BCO DA AMAZONIA S.A.</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>4155000009</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F663" t="n">
+        <v>92974996.94</v>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H663" t="n">
+        <v>9329</v>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J663" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>04902979</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>BCO DA AMAZONIA S.A.</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>8114000008</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F664" t="n">
+        <v>-2397872.61</v>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H664" t="n">
+        <v>9461</v>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J664" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>00000000</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>BCO DO BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>4155000009</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F665" t="n">
+        <v>287361213171.58</v>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H665" t="n">
+        <v>291</v>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J665" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>00000000</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>BCO DO BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>8114000008</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F666" t="n">
+        <v>-9713721199.950001</v>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H666" t="n">
+        <v>505</v>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J666" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>00000000</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>BCO DO BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>9090800008</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS REPASSADOS A ESTADOS E DISTRITO FEDERAL</t>
+        </is>
+      </c>
+      <c r="F667" t="n">
+        <v>62852309883.22</v>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H667" t="n">
+        <v>617</v>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>00000000</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>BCO DO BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>9090900001</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS REPASSADOS A MUNICÍPIOS</t>
+        </is>
+      </c>
+      <c r="F668" t="n">
+        <v>22413895321.71</v>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H668" t="n">
+        <v>618</v>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J668" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>13009717</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>BCO DO EST. DE SE S.A.</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>1899800001</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>(-) PROVISÃO PARA PERDAS DE CRÉDITO EM RESTITUIÇÃO DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS</t>
+        </is>
+      </c>
+      <c r="F669" t="n">
+        <v>-19448.45</v>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H669" t="n">
+        <v>15896</v>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J669" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>13009717</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>BCO DO EST. DE SE S.A.</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>4155000009</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F670" t="n">
+        <v>2061812921.55</v>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H670" t="n">
+        <v>16014</v>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J670" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>13009717</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>BCO DO EST. DE SE S.A.</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>8114000008</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F671" t="n">
+        <v>-64140462.92</v>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H671" t="n">
+        <v>16126</v>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J671" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>13009717</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>BCO DO EST. DE SE S.A.</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>9090800008</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS REPASSADOS A ESTADOS E DISTRITO FEDERAL</t>
+        </is>
+      </c>
+      <c r="F672" t="n">
+        <v>199288682.24</v>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H672" t="n">
+        <v>16201</v>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>13009717</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>BCO DO EST. DE SE S.A.</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>9090900001</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS REPASSADOS A MUNICÍPIOS</t>
+        </is>
+      </c>
+      <c r="F673" t="n">
+        <v>14024908.18</v>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H673" t="n">
+        <v>16202</v>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J673" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>04913711</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>BCO DO EST. DO PA S.A.</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>4155000009</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F674" t="n">
+        <v>304123.1</v>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H674" t="n">
+        <v>9758</v>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J674" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>04913711</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>BCO DO EST. DO PA S.A.</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>8114000008</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F675" t="n">
+        <v>-1413.57</v>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H675" t="n">
+        <v>9878</v>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>92702067</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>BCO DO ESTADO DO RS S.A.</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>4155000009</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F676" t="n">
+        <v>11040046942.05</v>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H676" t="n">
+        <v>49272</v>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J676" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>92702067</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>BCO DO ESTADO DO RS S.A.</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>8114000008</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F677" t="n">
+        <v>-312039802.39</v>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H677" t="n">
+        <v>49432</v>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J677" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>92702067</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>BCO DO ESTADO DO RS S.A.</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>9090800008</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS REPASSADOS A ESTADOS E DISTRITO FEDERAL</t>
+        </is>
+      </c>
+      <c r="F678" t="n">
+        <v>10306349442.94</v>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H678" t="n">
+        <v>49515</v>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J678" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>92702067</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>BCO DO ESTADO DO RS S.A.</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>9090900001</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS REPASSADOS A MUNICÍPIOS</t>
+        </is>
+      </c>
+      <c r="F679" t="n">
+        <v>113936934.05</v>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H679" t="n">
+        <v>49516</v>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J679" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>07237373</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>BCO DO NORDESTE DO BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>4155000009</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F680" t="n">
+        <v>208209265.49</v>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H680" t="n">
+        <v>10981</v>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J680" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>07237373</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>BCO DO NORDESTE DO BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>8114000008</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F681" t="n">
+        <v>-5292533.02</v>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H681" t="n">
+        <v>11136</v>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J681" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>17184037</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>BCO MERCANTIL DO BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>4155000009</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F682" t="n">
+        <v>894076.38</v>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H682" t="n">
+        <v>18565</v>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J682" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>17184037</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>BCO MERCANTIL DO BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>8114000008</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F683" t="n">
+        <v>-4065.53</v>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H683" t="n">
+        <v>18693</v>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J683" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>90400888</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>BCO SANTANDER (BRASIL) S.A.</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>4155000009</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F684" t="n">
+        <v>139996420.21</v>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H684" t="n">
+        <v>48396</v>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J684" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>90400888</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>BCO SANTANDER (BRASIL) S.A.</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>8114000008</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F685" t="n">
+        <v>-3635578.86</v>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H685" t="n">
+        <v>48605</v>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>00360305</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>CAIXA ECONOMICA FEDERAL</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>4155000009</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F686" t="n">
+        <v>135737572658.79</v>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H686" t="n">
+        <v>931</v>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J686" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>00360305</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>CAIXA ECONOMICA FEDERAL</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>8114000008</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F687" t="n">
+        <v>-3805410390.29</v>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H687" t="n">
+        <v>1132</v>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>00360305</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>CAIXA ECONOMICA FEDERAL</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>9090700005</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS REPASSADOS À UNIÃO</t>
+        </is>
+      </c>
+      <c r="F688" t="n">
+        <v>400845386107.65</v>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H688" t="n">
+        <v>1240</v>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>00360305</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>CAIXA ECONOMICA FEDERAL</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>9090800008</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS REPASSADOS A ESTADOS E DISTRITO FEDERAL</t>
+        </is>
+      </c>
+      <c r="F689" t="n">
+        <v>4597796002.82</v>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H689" t="n">
+        <v>1241</v>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>00360305</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>CAIXA ECONOMICA FEDERAL</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>9090900001</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS REPASSADOS A MUNICÍPIOS</t>
+        </is>
+      </c>
+      <c r="F690" t="n">
+        <v>1059811536.53</v>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H690" t="n">
+        <v>1242</v>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>60701190</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>ITAÚ UNIBANCO S.A.</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>4155000009</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F691" t="n">
+        <v>17593597.75</v>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H691" t="n">
+        <v>37964</v>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>60701190</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>ITAÚ UNIBANCO S.A.</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>8114000008</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F692" t="n">
+        <v>-467125.57</v>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>202604BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H692" t="n">
+        <v>38180</v>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>c3943538fe11afeb0a81d1b125b051e95ca0eced8cd76b1daeee1921948c70b9</t>
+        </is>
+      </c>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>50585090</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>BANCO BMG CONSIGNADO S.A.</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>1899800001</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>(-) PROVISÃO PARA PERDAS DE CRÉDITO EM RESTITUIÇÃO DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS</t>
+        </is>
+      </c>
+      <c r="F693" t="n">
+        <v>-386.23</v>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H693" t="n">
+        <v>32264</v>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>62421979</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>BANCO BMG SOLUÇÕES FINANCEIRAS S.A.</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>1899800001</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>(-) PROVISÃO PARA PERDAS DE CRÉDITO EM RESTITUIÇÃO DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS</t>
+        </is>
+      </c>
+      <c r="F694" t="n">
+        <v>-236.91</v>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H694" t="n">
+        <v>45450</v>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J694" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>92894922</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>BANCO ORIGINAL</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>1899800001</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>(-) PROVISÃO PARA PERDAS DE CRÉDITO EM RESTITUIÇÃO DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS</t>
+        </is>
+      </c>
+      <c r="F695" t="n">
+        <v>-4906.53</v>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H695" t="n">
+        <v>50216</v>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>28195667</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>BCO ABC BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>4155000009</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F696" t="n">
+        <v>1753305.48</v>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H696" t="n">
+        <v>21872</v>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J696" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>28195667</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>BCO ABC BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>8114000008</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F697" t="n">
+        <v>-57142.73</v>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H697" t="n">
+        <v>22017</v>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J697" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>28127603</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>BCO BANESTES S.A.</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>4155000009</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F698" t="n">
+        <v>4904891924.94</v>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H698" t="n">
+        <v>21116</v>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J698" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>28127603</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>BCO BANESTES S.A.</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>8114000008</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F699" t="n">
+        <v>-232751921.58</v>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H699" t="n">
+        <v>21251</v>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J699" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>28127603</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>BCO BANESTES S.A.</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>9090900001</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS REPASSADOS A MUNICÍPIOS</t>
+        </is>
+      </c>
+      <c r="F700" t="n">
+        <v>428365573.71</v>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H700" t="n">
+        <v>21327</v>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J700" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>61186680</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>BCO BMG S.A.</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>1899800001</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>(-) PROVISÃO PARA PERDAS DE CRÉDITO EM RESTITUIÇÃO DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS</t>
+        </is>
+      </c>
+      <c r="F701" t="n">
+        <v>-522680.49</v>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H701" t="n">
+        <v>41651</v>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J701" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>60746948</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>BCO BRADESCO S.A.</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>4155000009</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F702" t="n">
+        <v>283776803.35</v>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H702" t="n">
+        <v>38617</v>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J702" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>60746948</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>BCO BRADESCO S.A.</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>8114000008</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F703" t="n">
+        <v>-9284050.699999999</v>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H703" t="n">
+        <v>38830</v>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J703" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>04902979</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>BCO DA AMAZONIA S.A.</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>4155000009</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F704" t="n">
+        <v>90338336.5</v>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H704" t="n">
+        <v>9376</v>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J704" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>04902979</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>BCO DA AMAZONIA S.A.</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>8114000008</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F705" t="n">
+        <v>-2951559.95</v>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H705" t="n">
+        <v>9509</v>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J705" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>00000000</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>BCO DO BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>4155000009</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F706" t="n">
+        <v>283672414098.75</v>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H706" t="n">
+        <v>288</v>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J706" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>00000000</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>BCO DO BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>8114000008</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F707" t="n">
+        <v>-12257536052.96</v>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H707" t="n">
+        <v>501</v>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J707" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>00000000</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>BCO DO BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>9090800008</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS REPASSADOS A ESTADOS E DISTRITO FEDERAL</t>
+        </is>
+      </c>
+      <c r="F708" t="n">
+        <v>63016979705.95</v>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H708" t="n">
+        <v>613</v>
+      </c>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J708" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>00000000</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>BCO DO BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>9090900001</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS REPASSADOS A MUNICÍPIOS</t>
+        </is>
+      </c>
+      <c r="F709" t="n">
+        <v>22445376770.16</v>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H709" t="n">
+        <v>614</v>
+      </c>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J709" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>13009717</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>BCO DO EST. DE SE S.A.</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>1899800001</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>(-) PROVISÃO PARA PERDAS DE CRÉDITO EM RESTITUIÇÃO DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS</t>
+        </is>
+      </c>
+      <c r="F710" t="n">
+        <v>-19162.72</v>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H710" t="n">
+        <v>15990</v>
+      </c>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J710" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>13009717</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>BCO DO EST. DE SE S.A.</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>4155000009</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F711" t="n">
+        <v>2044543303.19</v>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H711" t="n">
+        <v>16109</v>
+      </c>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J711" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>13009717</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>BCO DO EST. DE SE S.A.</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>8114000008</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F712" t="n">
+        <v>-79123524.78</v>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H712" t="n">
+        <v>16221</v>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J712" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>13009717</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>BCO DO EST. DE SE S.A.</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>9090800008</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS REPASSADOS A ESTADOS E DISTRITO FEDERAL</t>
+        </is>
+      </c>
+      <c r="F713" t="n">
+        <v>198340109.33</v>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H713" t="n">
+        <v>16296</v>
+      </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J713" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>13009717</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>BCO DO EST. DE SE S.A.</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>9090900001</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS REPASSADOS A MUNICÍPIOS</t>
+        </is>
+      </c>
+      <c r="F714" t="n">
+        <v>14086282.82</v>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H714" t="n">
+        <v>16297</v>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J714" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>04913711</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>BCO DO EST. DO PA S.A.</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>4155000009</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F715" t="n">
+        <v>597092.5600000001</v>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H715" t="n">
+        <v>9809</v>
+      </c>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J715" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>04913711</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>BCO DO EST. DO PA S.A.</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>8114000008</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F716" t="n">
+        <v>-1748.73</v>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H716" t="n">
+        <v>9932</v>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J716" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>92702067</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>BCO DO ESTADO DO RS S.A.</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>4155000009</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F717" t="n">
+        <v>11046442326.66</v>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H717" t="n">
+        <v>49253</v>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J717" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>92702067</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>BCO DO ESTADO DO RS S.A.</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>8114000008</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F718" t="n">
+        <v>-390373703.05</v>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H718" t="n">
+        <v>49414</v>
+      </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J718" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>92702067</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>BCO DO ESTADO DO RS S.A.</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>9090800008</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS REPASSADOS A ESTADOS E DISTRITO FEDERAL</t>
+        </is>
+      </c>
+      <c r="F719" t="n">
+        <v>10306349442.94</v>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H719" t="n">
+        <v>49497</v>
+      </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J719" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>92702067</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>BCO DO ESTADO DO RS S.A.</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>9090900001</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS REPASSADOS A MUNICÍPIOS</t>
+        </is>
+      </c>
+      <c r="F720" t="n">
+        <v>116622047.86</v>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H720" t="n">
+        <v>49498</v>
+      </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J720" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>07237373</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>BCO DO NORDESTE DO BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>4155000009</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F721" t="n">
+        <v>210235899.58</v>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H721" t="n">
+        <v>11038</v>
+      </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J721" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>07237373</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>BCO DO NORDESTE DO BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>8114000008</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F722" t="n">
+        <v>-6669143.44</v>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H722" t="n">
+        <v>11193</v>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J722" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>17184037</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>BCO MERCANTIL DO BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>4155000009</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F723" t="n">
+        <v>900224.95</v>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H723" t="n">
+        <v>18703</v>
+      </c>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J723" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>17184037</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>BCO MERCANTIL DO BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>8114000008</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F724" t="n">
+        <v>-7010.15</v>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H724" t="n">
+        <v>18832</v>
+      </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J724" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>90400888</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>BCO SANTANDER (BRASIL) S.A.</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>4155000009</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F725" t="n">
+        <v>140601826.07</v>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H725" t="n">
+        <v>48366</v>
+      </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J725" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>90400888</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>BCO SANTANDER (BRASIL) S.A.</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>8114000008</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F726" t="n">
+        <v>-4547516.82</v>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H726" t="n">
+        <v>48574</v>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>00360305</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>CAIXA ECONOMICA FEDERAL</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>4155000009</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F727" t="n">
+        <v>131589294689.84</v>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H727" t="n">
+        <v>927</v>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J727" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>00360305</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>CAIXA ECONOMICA FEDERAL</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>8114000008</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F728" t="n">
+        <v>-4779349200.39</v>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H728" t="n">
+        <v>1127</v>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>00360305</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>CAIXA ECONOMICA FEDERAL</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>9090700005</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS REPASSADOS À UNIÃO</t>
+        </is>
+      </c>
+      <c r="F729" t="n">
+        <v>403449882590.66</v>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H729" t="n">
+        <v>1235</v>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J729" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>00360305</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>CAIXA ECONOMICA FEDERAL</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>9090800008</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS REPASSADOS A ESTADOS E DISTRITO FEDERAL</t>
+        </is>
+      </c>
+      <c r="F730" t="n">
+        <v>4618767253.95</v>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H730" t="n">
+        <v>1236</v>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>00360305</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>CAIXA ECONOMICA FEDERAL</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>9090900001</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS REPASSADOS A MUNICÍPIOS</t>
+        </is>
+      </c>
+      <c r="F731" t="n">
+        <v>1058263932.24</v>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H731" t="n">
+        <v>1237</v>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>60701190</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>ITAÚ UNIBANCO S.A.</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>4155000009</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F732" t="n">
+        <v>17705955.24</v>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H732" t="n">
+        <v>37923</v>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>60701190</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>ITAÚ UNIBANCO S.A.</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>8114000008</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS DE DEPÓSITOS JUDICIAIS E ADMINISTRATIVOS MANTIDOS NA INSTITUIÇÃO</t>
+        </is>
+      </c>
+      <c r="F733" t="n">
+        <v>-579483.0600000001</v>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>202605BANCOS.CSV</t>
+        </is>
+      </c>
+      <c r="H733" t="n">
+        <v>38142</v>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>955f305194219dc193f871ff537062c6bd562e723d4ad79087336ab4f5104056</t>
+        </is>
+      </c>
+      <c r="J733" t="inlineStr">
         <is>
           <t>BCB balancete doc. 4010</t>
         </is>
@@ -58296,7 +65244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58359,28 +65307,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00360305</t>
+          <t>04913711</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CAIXA ECONOMICA FEDERAL</t>
+          <t>BCO DO EST. DO PA S.A.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ampliado_sobre_pl</t>
+          <t>queda_brusca_3m</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.9796</v>
+        <v>-0.3477</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>-0.3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Estoque ampliado (mantido + repassado) superior a 3x o patrimonio liquido. Medida de escala e concentracao, nao estimativa automatica de perda.</t>
+          <t>Reducao superior a 30% do saldo mantido em 3 meses.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -58390,7 +65338,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>202603</t>
+          <t>202605</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -58412,34 +65360,38 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00000208</t>
+          <t>00360305</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BRB - BCO DE BRASILIA S.A.</t>
+          <t>CAIXA ECONOMICA FEDERAL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ausencia_ultima_base</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+          <t>ampliado_sobre_pl</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4.8367</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Instituicao ausente do balancete publico desde 202511. Possivel atraso de demonstracoes/balancetes — verificar razao junto a fontes primarias.</t>
+          <t>Estoque ampliado (mantido + repassado) superior a 3x o patrimonio liquido. Medida de escala e concentracao, nao estimativa automatica de perda.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>alta</t>
+          <t>media</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>202603</t>
+          <t>202605</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -58471,18 +65423,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mantidos_sobre_captacao</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0.3159</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.2</v>
-      </c>
+          <t>ausencia_ultima_base</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Depositos judiciais mantidos representam parcela relevante da captacao (dependencia de funding). Medida de escala, nao estimativa de perda. Dado defasado: ultima base disponivel da instituicao (202511), anterior a 202603.</t>
+          <t>Instituicao ausente do balancete publico desde 202511. Possivel atraso de demonstracoes/balancetes — verificar razao junto a fontes primarias.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -58492,7 +65440,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>202511</t>
+          <t>202605</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -58524,41 +65472,94 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>mantidos_sobre_captacao</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Depositos judiciais mantidos representam parcela relevante da captacao (dependencia de funding). Medida de escala, nao estimativa de perda. Dado defasado: ultima base disponivel da instituicao (202511), anterior a 202605.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>202511</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>sinal_para_investigacao</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Red flag e sinal para investigacao e nao prova de irregularidade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>00000208</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BRB - BCO DE BRASILIA S.A.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>ampliado_sobre_pl</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D6" t="n">
         <v>7.9442</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E6" t="n">
         <v>3</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Estoque ampliado (mantido + repassado) superior a 3x o patrimonio liquido. Medida de escala e concentracao, nao estimativa automatica de perda. Dado defasado: ultima base disponivel da instituicao (202511), anterior a 202603.</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Estoque ampliado (mantido + repassado) superior a 3x o patrimonio liquido. Medida de escala e concentracao, nao estimativa automatica de perda. Dado defasado: ultima base disponivel da instituicao (202511), anterior a 202605.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>alta</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>202511</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>BCB balancete doc. 4010</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>BCB balancete doc. 4010</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>sinal_para_investigacao</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Red flag e sinal para investigacao e nao prova de irregularidade.</t>
         </is>
@@ -58636,7 +65637,7 @@
         <v>29985701420.66</v>
       </c>
       <c r="F2" t="n">
-        <v>202603</v>
+        <v>202605</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
